--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2017_T1_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2017_T1_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.336</t>
-  </si>
-  <si>
-    <t>(0.183)</t>
-  </si>
-  <si>
-    <t>7.088</t>
-  </si>
-  <si>
-    <t>(0.854)</t>
-  </si>
-  <si>
-    <t>43.520</t>
-  </si>
-  <si>
-    <t>(9.602)</t>
-  </si>
-  <si>
-    <t>51.754</t>
-  </si>
-  <si>
-    <t>(11.685)</t>
-  </si>
-  <si>
-    <t>1.827</t>
-  </si>
-  <si>
-    <t>(0.375)</t>
-  </si>
-  <si>
-    <t>8.143</t>
-  </si>
-  <si>
-    <t>(0.887)</t>
-  </si>
-  <si>
-    <t>2.251</t>
-  </si>
-  <si>
-    <t>(0.453)</t>
-  </si>
-  <si>
-    <t>2.820</t>
-  </si>
-  <si>
-    <t>(2.335)</t>
-  </si>
-  <si>
-    <t>57.911</t>
-  </si>
-  <si>
-    <t>(11.033)</t>
-  </si>
-  <si>
-    <t>47.478</t>
-  </si>
-  <si>
-    <t>(13.055)</t>
+    <t>1.397</t>
+  </si>
+  <si>
+    <t>(0.188)</t>
+  </si>
+  <si>
+    <t>7.414</t>
+  </si>
+  <si>
+    <t>(0.877)</t>
+  </si>
+  <si>
+    <t>33.448</t>
+  </si>
+  <si>
+    <t>(6.168)</t>
+  </si>
+  <si>
+    <t>39.001</t>
+  </si>
+  <si>
+    <t>(6.788)</t>
+  </si>
+  <si>
+    <t>1.596</t>
+  </si>
+  <si>
+    <t>(0.254)</t>
+  </si>
+  <si>
+    <t>8.494</t>
+  </si>
+  <si>
+    <t>(0.910)</t>
+  </si>
+  <si>
+    <t>2.056</t>
+  </si>
+  <si>
+    <t>(0.430)</t>
+  </si>
+  <si>
+    <t>0.504</t>
+  </si>
+  <si>
+    <t>(0.100)</t>
+  </si>
+  <si>
+    <t>47.337</t>
+  </si>
+  <si>
+    <t>(7.424)</t>
+  </si>
+  <si>
+    <t>31.639</t>
+  </si>
+  <si>
+    <t>(6.413)</t>
   </si>
   <si>
     <t>23</t>
@@ -198,7 +198,7 @@
     <t>(16.107)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.742*</t>
-  </si>
-  <si>
-    <t>0.521</t>
-  </si>
-  <si>
-    <t>32.071</t>
-  </si>
-  <si>
-    <t>29.819</t>
-  </si>
-  <si>
-    <t>-0.324</t>
-  </si>
-  <si>
-    <t>-1.447</t>
-  </si>
-  <si>
-    <t>-0.312</t>
-  </si>
-  <si>
-    <t>-2.358</t>
-  </si>
-  <si>
-    <t>41.671*</t>
-  </si>
-  <si>
-    <t>17.619</t>
+    <t>0.681</t>
+  </si>
+  <si>
+    <t>0.195</t>
+  </si>
+  <si>
+    <t>42.143***</t>
+  </si>
+  <si>
+    <t>42.572**</t>
+  </si>
+  <si>
+    <t>-0.093</t>
+  </si>
+  <si>
+    <t>-1.799</t>
+  </si>
+  <si>
+    <t>-0.117</t>
+  </si>
+  <si>
+    <t>-0.042</t>
+  </si>
+  <si>
+    <t>52.245***</t>
+  </si>
+  <si>
+    <t>33.458**</t>
   </si>
 </sst>
 </file>
